--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487815_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487815_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.131</v>
+        <v>1.9166</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5848</v>
+        <v>2.3705</v>
       </c>
       <c r="F2" t="n">
         <v>-0.4539</v>
@@ -610,10 +610,10 @@
         <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5063</v>
+        <v>0.2919</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4658</v>
+        <v>0.2515</v>
       </c>
       <c r="U2" t="n">
         <v>0.0405</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. TAIWO</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2337</v>
+        <v>1.0505</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1547</v>
+        <v>4.6281</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.921</v>
+        <v>-3.5776</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.2184</v>
+        <v>3.1983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3415</v>
+        <v>4.0767</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8769</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3894</v>
+        <v>4.9537</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4678</v>
+        <v>4.3749</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0784</v>
+        <v>0.5788</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.829</v>
+        <v>-1.7555</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1263</v>
+        <v>-0.2982</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9553</v>
+        <v>-1.4573</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1379</v>
+        <v>-0.2081</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8542</v>
+        <v>0.152</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7163</v>
+        <v>-0.3601</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6899</v>
+        <v>-3.3965</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6899</v>
+        <v>-0.4776</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>S. TAIWO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2455</v>
+        <v>-0.3443</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7056</v>
+        <v>1.5473</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.4601</v>
+        <v>-1.8916</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1983</v>
+        <v>-2.2184</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0767</v>
+        <v>-0.3415</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8784999999999999</v>
+        <v>-1.8769</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9537</v>
+        <v>-0.3894</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3749</v>
+        <v>-0.4678</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5788</v>
+        <v>0.0784</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7555</v>
+        <v>-1.829</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2982</v>
+        <v>0.1263</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4573</v>
+        <v>-1.9553</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0132</v>
+        <v>0.5599</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7705</v>
+        <v>1.2469</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2426</v>
+        <v>-0.6869</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.3965</v>
+        <v>0.6899</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4776</v>
+        <v>0.6899</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.9188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1399</v>
+        <v>-1.0159</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.619</v>
+        <v>-0.5538</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5209</v>
+        <v>-0.4621</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0608</v>
@@ -844,13 +844,13 @@
         <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.5389</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2577</v>
+        <v>0.3229</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9205</v>
+        <v>-0.8618</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>J. HANNA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3063</v>
+        <v>-2.0301</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7301</v>
+        <v>2.0131</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.0364</v>
+        <v>-4.0432</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3285</v>
+        <v>-1.0803</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0022</v>
+        <v>1.7739</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6737</v>
+        <v>-2.8542</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2554</v>
+        <v>2.3571</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9698</v>
+        <v>2.3661</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7144</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-3.4374</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0324</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9593</v>
+        <v>-2.8452</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.2487</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1789</v>
+        <v>-0.5335</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5559</v>
+        <v>0.5696</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.377</v>
+        <v>-1.1032</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.565</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.565</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. HANNA</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3493</v>
+        <v>-2.2239</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8407</v>
+        <v>0.9401</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.19</v>
+        <v>-3.164</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0803</v>
+        <v>-1.5884</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7739</v>
+        <v>3.0211</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.8542</v>
+        <v>-4.6095</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3571</v>
+        <v>1.155</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3661</v>
+        <v>3.5602</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-2.4052</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.4374</v>
+        <v>-2.7434</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.5391</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.8452</v>
+        <v>-2.2043</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4162</v>
+        <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8527</v>
+        <v>-0.5917</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3972</v>
+        <v>0.242</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2499</v>
+        <v>-0.8337</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1675</v>
+        <v>0.5838</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.659</v>
+        <v>-2.4613</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4463</v>
+        <v>-0.4471</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1053</v>
+        <v>-2.0142</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5884</v>
+        <v>0.2327</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0211</v>
+        <v>-0.2922</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.6095</v>
+        <v>0.525</v>
       </c>
       <c r="J8" t="n">
-        <v>1.155</v>
+        <v>1.6699</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5602</v>
+        <v>-0.1328</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.4052</v>
+        <v>1.8027</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7434</v>
+        <v>-1.4371</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5391</v>
+        <v>-0.1595</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.2043</v>
+        <v>-1.2777</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4162</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0269</v>
+        <v>-0.1134</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2519</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.775</v>
+        <v>-0.6582</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4599</v>
+        <v>-0.7076</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5838</v>
+        <v>0.4599</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0437</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2066</v>
+        <v>-2.5387</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8401</v>
+        <v>0.9381</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3665</v>
+        <v>-3.4768</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2327</v>
+        <v>1.3285</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2922</v>
+        <v>3.0022</v>
       </c>
       <c r="I9" t="n">
-        <v>0.525</v>
+        <v>-1.6737</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6699</v>
+        <v>2.2554</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1328</v>
+        <v>2.9698</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8027</v>
+        <v>-0.7144</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4371</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1595</v>
+        <v>0.0324</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2777</v>
+        <v>-0.9593</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8731</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8587</v>
+        <v>-0.0535</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8482</v>
+        <v>0.7639</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0105</v>
+        <v>-0.8174</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7076</v>
+        <v>-2.565</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2648</v>
+        <v>-5.3426</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9322</v>
+        <v>-5.0394</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3326</v>
+        <v>-0.3033</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8856</v>
@@ -1234,13 +1234,13 @@
         <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4887</v>
+        <v>0.4109</v>
       </c>
       <c r="T10" t="n">
-        <v>0.531</v>
+        <v>0.4239</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0424</v>
+        <v>-0.013</v>
       </c>
       <c r="V10" t="n">
         <v>1.7513</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.3157</v>
+        <v>-12.9897</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0709</v>
+        <v>6.3969</v>
       </c>
       <c r="F11" t="n">
         <v>-19.3867</v>
@@ -1303,7 +1303,7 @@
         <v>-12.7972</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.2435</v>
+        <v>-6.243500000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>-15.6089</v>
@@ -1312,13 +1312,13 @@
         <v>9.365399999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1025</v>
+        <v>-0.7764</v>
       </c>
       <c r="T11" t="n">
-        <v>4.1912</v>
+        <v>4.5176</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.2937</v>
+        <v>-5.2938</v>
       </c>
       <c r="V11" t="n">
         <v>-3.6441</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.5557</v>
+        <v>10.547</v>
       </c>
       <c r="E12" t="n">
-        <v>10.1549</v>
+        <v>10.7979</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5992</v>
+        <v>-0.2509</v>
       </c>
       <c r="G12" t="n">
         <v>6.5245</v>
@@ -1390,13 +1390,13 @@
         <v>2.0812</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3851</v>
+        <v>-0.3937</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5624</v>
+        <v>0.0805</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8226</v>
+        <v>-0.4743</v>
       </c>
       <c r="V12" t="n">
         <v>2.3351</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.492</v>
+        <v>9.262700000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>7.2098</v>
+        <v>8.6028</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2822</v>
+        <v>0.6599</v>
       </c>
       <c r="G13" t="n">
         <v>5.4726</v>
@@ -1468,13 +1468,13 @@
         <v>2.9137</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7289</v>
+        <v>0.0419</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6029</v>
+        <v>0.7902</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.126</v>
+        <v>-0.7482</v>
       </c>
       <c r="V13" t="n">
         <v>1.8751</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>N. RAKOCEVIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2388</v>
+        <v>1.6856</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2223</v>
+        <v>0.7065</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0165</v>
+        <v>0.9791</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.7241</v>
+        <v>0.8757</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.8251</v>
+        <v>0.0895</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.899</v>
+        <v>0.7862</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.0539</v>
+        <v>0.6879</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2243</v>
+        <v>0.1875</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.8296</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.6702</v>
+        <v>0.1877</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.6008</v>
+        <v>-0.098</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0694</v>
+        <v>0.2857</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0877</v>
+        <v>-0.0225</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7112</v>
+        <v>0.0186</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3765</v>
+        <v>-0.0411</v>
       </c>
       <c r="V14" t="n">
-        <v>3.6264</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.565</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.0614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.069</v>
+        <v>1.3101</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9173</v>
+        <v>-0.0471</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1518</v>
+        <v>1.3573</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4366</v>
@@ -1624,13 +1624,13 @@
         <v>2.7055</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2767</v>
+        <v>0.5178</v>
       </c>
       <c r="T15" t="n">
-        <v>2.177</v>
+        <v>1.2126</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9003</v>
+        <v>-0.6948</v>
       </c>
       <c r="V15" t="n">
         <v>1.6452</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. RAKOCEVIC</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5594</v>
+        <v>1.107</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4922</v>
+        <v>1.4722</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0672</v>
+        <v>-0.3652</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8757</v>
+        <v>-4.7241</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0895</v>
+        <v>-2.8251</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7862</v>
+        <v>-1.899</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6879</v>
+        <v>-2.0539</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1875</v>
+        <v>-0.2243</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5004999999999999</v>
+        <v>-1.8296</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1877</v>
+        <v>-2.6702</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.098</v>
+        <v>-2.6008</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2857</v>
+        <v>-0.0694</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1487</v>
+        <v>0.9559</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1957</v>
+        <v>0.9611</v>
       </c>
       <c r="U16" t="n">
-        <v>0.047</v>
+        <v>-0.0052</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3.6264</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.565</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.0614</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3749</v>
+        <v>-1.1058</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1174</v>
+        <v>0.0969</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2575</v>
+        <v>-1.2027</v>
       </c>
       <c r="G17" t="n">
         <v>2.3424</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>0.137</v>
+        <v>0.4061</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5434</v>
+        <v>0.7577</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4064</v>
+        <v>-0.3516</v>
       </c>
       <c r="V17" t="n">
         <v>-1.9813</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4779</v>
+        <v>-1.451</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3072</v>
+        <v>-0.6286</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1708</v>
+        <v>-0.8224</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6179</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3699</v>
+        <v>0.3968</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9473</v>
+        <v>0.6258</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5774</v>
+        <v>-0.229</v>
       </c>
       <c r="V18" t="n">
         <v>-0.23</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.757</v>
+        <v>-1.4688</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4164</v>
+        <v>-1.0949</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3406</v>
+        <v>-0.3739</v>
       </c>
       <c r="G19" t="n">
         <v>-2.9816</v>
@@ -1936,13 +1936,13 @@
         <v>2.0812</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8566</v>
+        <v>-0.5684</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2519</v>
+        <v>0.0696</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6047</v>
+        <v>-0.638</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9822</v>
+        <v>-2.8893</v>
       </c>
       <c r="E20" t="n">
-        <v>1.551</v>
+        <v>0.9081</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.5332</v>
+        <v>-3.7974</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8067</v>
@@ -2014,13 +2014,13 @@
         <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>1.554</v>
+        <v>0.6469</v>
       </c>
       <c r="T20" t="n">
-        <v>1.323</v>
+        <v>0.6801</v>
       </c>
       <c r="U20" t="n">
-        <v>0.231</v>
+        <v>-0.0332</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1051</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0071</v>
+        <v>-2.9674</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.32</v>
+        <v>-1.4271</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6871</v>
+        <v>-1.5403</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3227</v>
@@ -2092,13 +2092,13 @@
         <v>2.0812</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2036</v>
+        <v>-0.1639</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2048</v>
+        <v>0.0977</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4084</v>
+        <v>-0.2616</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5213</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>13.3158</v>
+        <v>14.0301</v>
       </c>
       <c r="E22" t="n">
-        <v>19.3865</v>
+        <v>19.3867</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.0707</v>
+        <v>-5.3565</v>
       </c>
       <c r="G22" t="n">
         <v>2.3256</v>
@@ -2170,13 +2170,13 @@
         <v>15.6089</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1024</v>
+        <v>1.8169</v>
       </c>
       <c r="T22" t="n">
-        <v>5.2938</v>
+        <v>5.2939</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.1913</v>
+        <v>-3.477</v>
       </c>
       <c r="V22" t="n">
         <v>3.6441</v>
